--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0001T0006Z000C1N39_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0001T0006Z000C1N39_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>22.36260343901156</v>
+        <v>3.633923058839379</v>
       </c>
       <c r="D2" t="n">
-        <v>22.31412942205701</v>
+        <v>3.626046031084265</v>
       </c>
       <c r="E2" t="n">
-        <v>6.575112669980451</v>
+        <v>1.068455808871823</v>
       </c>
       <c r="F2" t="n">
-        <v>6.461318232517319</v>
+        <v>1.049964212784064</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>29.67758391325182</v>
+        <v>4.822607385903422</v>
       </c>
       <c r="D3" t="n">
-        <v>29.78027091652365</v>
+        <v>4.839294023935094</v>
       </c>
       <c r="E3" t="n">
-        <v>6.575112669980451</v>
+        <v>1.068455808871823</v>
       </c>
       <c r="F3" t="n">
-        <v>6.461318232517319</v>
+        <v>1.049964212784064</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>37.68587496002061</v>
+        <v>6.123954681003348</v>
       </c>
       <c r="D4" t="n">
-        <v>37.3367940765806</v>
+        <v>6.067229037444347</v>
       </c>
       <c r="E4" t="n">
-        <v>6.575112669980451</v>
+        <v>1.068455808871823</v>
       </c>
       <c r="F4" t="n">
-        <v>6.461318232517319</v>
+        <v>1.049964212784064</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>21.31047148448082</v>
+        <v>3.462951616228133</v>
       </c>
       <c r="D5" t="n">
-        <v>21.31310876101809</v>
+        <v>3.46338017366544</v>
       </c>
       <c r="E5" t="n">
-        <v>6.575112669980451</v>
+        <v>1.068455808871823</v>
       </c>
       <c r="F5" t="n">
-        <v>6.461318232517319</v>
+        <v>1.049964212784064</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
